--- a/docs/ボディ見える化_PLCデバイス_20260709.xlsx
+++ b/docs/ボディ見える化_PLCデバイス_20260709.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phuon\Downloads\Chrome\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myProgram\GitHub\body_inspect_visualize_coba\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B9A9F3-7123-4599-8ABB-15F354505204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22423CC5-B044-4F75-97AF-834843281E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4657B025-33E1-4D12-9C02-57E9F5466666}"/>
   </bookViews>
@@ -439,7 +439,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -497,23 +497,8 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -529,12 +514,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -617,7 +596,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -648,7 +627,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -660,22 +639,16 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -801,9 +774,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -841,7 +814,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -947,7 +920,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1089,7 +1062,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1326,13 +1299,13 @@
       <c r="E21" s="9"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="4" t="s">
         <v>50</v>
       </c>
       <c r="E22" s="9"/>
@@ -1341,10 +1314,10 @@
       <c r="B23" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="4" t="s">
         <v>51</v>
       </c>
       <c r="E23" s="9"/>
@@ -1353,10 +1326,10 @@
       <c r="B24" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="4" t="s">
         <v>52</v>
       </c>
       <c r="E24" s="9"/>
@@ -1365,10 +1338,10 @@
       <c r="B25" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="4" t="s">
         <v>53</v>
       </c>
       <c r="E25" s="9"/>
@@ -1377,10 +1350,10 @@
       <c r="B26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="4" t="s">
         <v>54</v>
       </c>
       <c r="E26" s="9"/>
@@ -1389,10 +1362,10 @@
       <c r="B27" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="4" t="s">
         <v>55</v>
       </c>
       <c r="E27" s="9"/>
@@ -1401,10 +1374,10 @@
       <c r="B28" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="4" t="s">
         <v>68</v>
       </c>
       <c r="E28" s="9"/>

--- a/docs/ボディ見える化_PLCデバイス_20260709.xlsx
+++ b/docs/ボディ見える化_PLCデバイス_20260709.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myProgram\GitHub\body_inspect_visualize_coba\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22423CC5-B044-4F75-97AF-834843281E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395906B8-C51D-4647-83E1-F3751DA60697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4657B025-33E1-4D12-9C02-57E9F5466666}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="77">
   <si>
     <t>機能</t>
     <rPh sb="0" eb="2">
@@ -430,6 +430,52 @@
   </si>
   <si>
     <t>B15</t>
+  </si>
+  <si>
+    <t>アラーム履歴データ</t>
+    <rPh sb="4" eb="6">
+      <t>リレキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日時(2W)</t>
+    <rPh sb="0" eb="2">
+      <t>ニチジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EM11000-EM11999</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EM12000-EM12999</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例) LR10.5 → 1005</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>経過秒形式(基準=2000/1/1 00:00:00)</t>
+    <rPh sb="0" eb="3">
+      <t>ケイカビョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アラームデバイス(2W)</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1073,7 +1119,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:E31"/>
+  <dimension ref="B2:E33"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
@@ -1386,7 +1432,31 @@
       <c r="B30" s="5"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B31" s="5"/>
+      <c r="B31" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="B32" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B33" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" t="s">
+        <v>74</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
